--- a/testcases/locations/location-notes.xlsx
+++ b/testcases/locations/location-notes.xlsx
@@ -3400,7 +3400,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Manual</t>
+          <t xml:space="preserve">Automated</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10888,12 +10888,12 @@
       <c r="G341" s="2" t="inlineStr"/>
       <c r="H341" s="2" t="inlineStr">
         <is>
-          <t>Automated: 55 / Pending: 0</t>
+          <t xml:space="preserve">Automated: 58 / Pending: 0</t>
         </is>
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>Pass:54 Fail:0 Skipped:0 Blocked:1</t>
+          <t xml:space="preserve">Pass:57 Fail:0 Skipped:0 Blocked:1</t>
         </is>
       </c>
       <c r="J341" s="2" t="inlineStr"/>
